--- a/Result/profitability/4121.xlsx
+++ b/Result/profitability/4121.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06375</v>
+        <v>-0.07125000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>32.80875</v>
+        <v>32.76374999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06875000000000001</v>
+        <v>-0.07375000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>31.21875</v>
+        <v>31.30875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0425</v>
+        <v>-0.0525</v>
       </c>
       <c r="N4" t="n">
-        <v>30.35625</v>
+        <v>30.245</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.11625</v>
+        <v>-0.13375</v>
       </c>
       <c r="N5" t="n">
-        <v>27.66375</v>
+        <v>27.54375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.12</v>
+        <v>-0.13375</v>
       </c>
       <c r="N6" t="n">
-        <v>27.06625</v>
+        <v>26.9675</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.12125</v>
+        <v>-0.13625</v>
       </c>
       <c r="N7" t="n">
-        <v>26.24375</v>
+        <v>26.26625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08499999999999999</v>
+        <v>-0.09625</v>
       </c>
       <c r="N8" t="n">
-        <v>25.78875</v>
+        <v>25.77375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.63</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007500000000000007</v>
+        <v>0.007499999999999993</v>
       </c>
       <c r="N9" t="n">
         <v>25.73</v>
@@ -1645,7 +1645,7 @@
         <v>0.19</v>
       </c>
       <c r="M10" t="n">
-        <v>1.040834085586084e-17</v>
+        <v>-3.469446951953614e-18</v>
       </c>
       <c r="N10" t="n">
         <v>26.47125</v>
@@ -1772,7 +1772,7 @@
         <v>0.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07250000000000001</v>
+        <v>0.0725</v>
       </c>
       <c r="N11" t="n">
         <v>27.80375</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4121</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>947</v>
+      </c>
+      <c r="D75" t="n">
+        <v>627</v>
+      </c>
+      <c r="E75" t="n">
+        <v>320</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.03749999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.09000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8181818181818183</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1200000000000045</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.003541912632821886</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9600000000000009</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02764976958525345</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
